--- a/apps-script/Estructura_PreGenerada.xlsx
+++ b/apps-script/Estructura_PreGenerada.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
           <t>Categoria</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Chip</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -462,6 +467,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -484,6 +490,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -506,6 +513,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -528,6 +536,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -550,6 +559,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -572,6 +582,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -594,6 +605,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -616,6 +628,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -638,6 +651,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -660,6 +674,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,6 +697,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -704,6 +720,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -726,6 +743,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -748,6 +766,7 @@
           <t>Televisores</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -770,6 +789,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -792,6 +812,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -814,6 +835,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -836,6 +858,7 @@
           <t>Televisores</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -858,6 +881,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -880,6 +904,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -902,6 +927,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -924,6 +950,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -946,6 +973,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -968,6 +996,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -990,6 +1019,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1012,6 +1042,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1034,6 +1065,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1056,6 +1088,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1078,6 +1111,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1100,6 +1134,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1122,6 +1161,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1144,6 +1184,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1166,6 +1207,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1188,6 +1230,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1210,6 +1253,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1232,6 +1276,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1254,6 +1299,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1276,6 +1322,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1298,6 +1345,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1320,6 +1368,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1342,6 +1391,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1364,6 +1418,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1386,6 +1441,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1408,6 +1464,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1430,6 +1487,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1452,6 +1510,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1474,6 +1533,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1496,6 +1556,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1518,6 +1579,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1540,6 +1602,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1562,6 +1625,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1584,6 +1648,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1606,6 +1671,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1628,6 +1694,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1650,6 +1717,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1672,6 +1740,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1694,6 +1763,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1716,6 +1786,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1738,6 +1809,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1760,6 +1832,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1782,6 +1855,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1804,6 +1878,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1826,6 +1901,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1848,6 +1924,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1870,6 +1947,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1892,6 +1970,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1914,6 +1993,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1936,6 +2016,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1958,6 +2039,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1980,6 +2062,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2002,6 +2085,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2024,6 +2108,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2046,6 +2131,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2068,6 +2154,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2090,6 +2177,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2112,6 +2200,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2134,6 +2223,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2156,6 +2246,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2178,6 +2273,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1 SIM</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2200,6 +2300,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2222,6 +2327,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2244,6 +2350,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2266,6 +2373,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2288,6 +2400,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2310,6 +2427,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2332,6 +2450,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2354,6 +2473,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2376,6 +2500,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2398,6 +2523,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2420,6 +2546,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2442,6 +2569,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2464,6 +2596,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2486,6 +2619,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2508,6 +2642,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2530,6 +2665,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2552,6 +2688,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2574,6 +2711,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2596,6 +2738,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2618,6 +2761,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2640,6 +2788,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2662,6 +2815,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2684,6 +2842,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2706,6 +2869,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2728,6 +2896,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2750,6 +2919,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2772,6 +2942,7 @@
           <t>Computadoras</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2794,6 +2965,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2816,6 +2992,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2838,6 +3015,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2860,6 +3042,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2882,6 +3069,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2904,6 +3092,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2926,6 +3119,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2948,6 +3146,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2970,6 +3173,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2992,6 +3196,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3014,6 +3223,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3036,6 +3246,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3058,6 +3273,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3080,6 +3300,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3102,6 +3327,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3124,6 +3354,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3146,6 +3377,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3168,6 +3404,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3190,6 +3431,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3212,6 +3454,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3234,6 +3481,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3256,6 +3504,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3278,6 +3527,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3300,6 +3550,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3322,6 +3573,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3344,6 +3600,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3366,6 +3627,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3388,6 +3654,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3410,6 +3681,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3432,6 +3704,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3454,6 +3727,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3476,6 +3754,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3498,6 +3781,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3520,6 +3804,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3542,6 +3831,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3564,6 +3858,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3586,6 +3885,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3608,6 +3912,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3630,6 +3939,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3652,6 +3966,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3674,6 +3993,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3696,6 +4016,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3718,6 +4039,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3740,6 +4062,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3762,6 +4085,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3784,6 +4108,7 @@
           <t>Relojes</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3806,6 +4131,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3828,6 +4158,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3850,6 +4185,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3872,6 +4212,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3894,6 +4239,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3916,6 +4266,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3938,6 +4293,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3960,6 +4320,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3982,6 +4347,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4004,6 +4374,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4026,6 +4401,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4048,6 +4424,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4070,6 +4447,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4092,6 +4474,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4114,6 +4501,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4136,6 +4528,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4158,6 +4555,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4180,6 +4582,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4202,6 +4609,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4224,6 +4636,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4246,6 +4663,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4268,6 +4690,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1 SIM</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4290,6 +4717,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1 SIM</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4312,6 +4744,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4334,6 +4771,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4356,6 +4798,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4378,6 +4825,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4400,6 +4848,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4422,6 +4875,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4444,6 +4902,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4466,6 +4929,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4488,6 +4956,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4510,6 +4983,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4532,6 +5010,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4554,6 +5037,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4576,6 +5064,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4598,6 +5087,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4620,6 +5114,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4642,6 +5141,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4664,6 +5168,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4686,6 +5195,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4708,6 +5222,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4730,6 +5249,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4752,6 +5276,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4774,6 +5303,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4796,6 +5330,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4818,6 +5357,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4840,6 +5384,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>1 SIM</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4862,6 +5411,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>1 SIM</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4884,6 +5438,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4906,6 +5465,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4928,6 +5492,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4950,6 +5515,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4972,6 +5542,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4994,6 +5565,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5016,6 +5592,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5038,6 +5619,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5060,6 +5646,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5082,6 +5673,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5104,6 +5700,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5126,6 +5727,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5148,6 +5754,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5170,6 +5781,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5192,6 +5808,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5214,6 +5835,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5236,6 +5862,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5258,6 +5889,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5280,6 +5916,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>1 SIM</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5302,6 +5943,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5324,6 +5970,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5346,6 +5997,7 @@
           <t>Consolas</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5368,6 +6020,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5390,6 +6047,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5412,6 +6074,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5434,6 +6101,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5456,6 +6128,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5478,6 +6155,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5500,6 +6182,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5522,6 +6209,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5544,6 +6236,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5566,6 +6259,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5588,6 +6286,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5610,6 +6313,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5632,6 +6340,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5654,6 +6367,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5676,6 +6394,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5698,6 +6421,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5720,6 +6448,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5742,6 +6475,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5764,6 +6502,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5786,6 +6529,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5808,6 +6556,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5830,6 +6583,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5852,6 +6610,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5874,6 +6637,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5896,6 +6664,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5918,6 +6691,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5940,6 +6718,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5962,6 +6745,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5984,6 +6772,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6006,6 +6799,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6028,6 +6826,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6050,6 +6853,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6072,6 +6880,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6094,6 +6907,7 @@
           <t>Audio</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6116,6 +6930,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6138,6 +6957,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6160,6 +6984,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6182,6 +7011,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6204,6 +7038,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6226,6 +7065,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6248,6 +7092,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>1 SIM</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6270,6 +7119,7 @@
           <t>Tablets</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6292,6 +7142,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6314,6 +7169,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6336,6 +7196,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6358,6 +7223,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6380,6 +7250,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6402,6 +7277,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6424,6 +7304,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6446,6 +7331,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6468,6 +7358,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6490,6 +7385,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>eSIM</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6512,6 +7412,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6534,6 +7439,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6556,6 +7466,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6578,6 +7493,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6600,6 +7520,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6622,6 +7547,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6644,6 +7574,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6666,6 +7601,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6688,6 +7628,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6710,6 +7655,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6732,6 +7682,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6754,6 +7709,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6776,6 +7736,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6798,6 +7763,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6820,6 +7790,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6842,6 +7817,7 @@
           <t>Accesorios</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6864,6 +7840,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6886,6 +7867,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6908,6 +7894,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6930,6 +7921,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6952,6 +7948,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6974,6 +7975,11 @@
           <t>Celulares</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Dual SIM</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6994,6 +8000,11 @@
       <c r="D299" t="inlineStr">
         <is>
           <t>Celulares</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>eSIM</t>
         </is>
       </c>
     </row>

--- a/apps-script/Estructura_PreGenerada.xlsx
+++ b/apps-script/Estructura_PreGenerada.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Diccionario_Almacenamientos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Diccionario_Colores" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Precios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Imagenes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9067,7 +9068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G404"/>
+  <dimension ref="A1:F404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9101,11 +9102,6 @@
           <t>Precio Cliente Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Imagen</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9126,7 +9122,6 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9147,7 +9142,6 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9168,7 +9162,6 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9189,7 +9182,6 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9210,7 +9202,6 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9231,7 +9222,6 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9252,7 +9242,6 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9273,7 +9262,6 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9294,7 +9282,6 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9315,7 +9302,6 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9336,7 +9322,6 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9357,7 +9342,6 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9378,7 +9362,6 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9399,7 +9382,6 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9420,7 +9402,6 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9441,7 +9422,6 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9462,7 +9442,6 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9483,7 +9462,6 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9504,7 +9482,6 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9525,7 +9502,6 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9546,7 +9522,6 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9567,7 +9542,6 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9588,7 +9562,6 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9609,7 +9582,6 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9630,7 +9602,6 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9651,7 +9622,6 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,7 +9642,6 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9693,7 +9662,6 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9714,7 +9682,6 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9735,7 +9702,6 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9756,7 +9722,6 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9777,7 +9742,6 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9798,7 +9762,6 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9819,7 +9782,6 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9840,7 +9802,6 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9861,7 +9822,6 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9882,7 +9842,6 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9903,7 +9862,6 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9924,7 +9882,6 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9945,7 +9902,6 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9966,7 +9922,6 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9987,7 +9942,6 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10008,7 +9962,6 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10029,7 +9982,6 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10050,7 +10002,6 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10071,7 +10022,6 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10092,7 +10042,6 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10113,7 +10062,6 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10134,7 +10082,6 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10155,7 +10102,6 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10176,7 +10122,6 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10197,7 +10142,6 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10218,7 +10162,6 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10239,7 +10182,6 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10260,7 +10202,6 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10281,7 +10222,6 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -10302,7 +10242,6 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10323,7 +10262,6 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10344,7 +10282,6 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10365,7 +10302,6 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10386,7 +10322,6 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10407,7 +10342,6 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10428,7 +10362,6 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10449,7 +10382,6 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10470,7 +10402,6 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10491,7 +10422,6 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10512,7 +10442,6 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10533,7 +10462,6 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10554,7 +10482,6 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10575,7 +10502,6 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10596,7 +10522,6 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10617,7 +10542,6 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10638,7 +10562,6 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10659,7 +10582,6 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10680,7 +10602,6 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10701,7 +10622,6 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10722,7 +10642,6 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10743,7 +10662,6 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10764,7 +10682,6 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10785,7 +10702,6 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10806,7 +10722,6 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10827,7 +10742,6 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10848,7 +10762,6 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10869,7 +10782,6 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10890,7 +10802,6 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10911,7 +10822,6 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10928,7 +10838,6 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10945,7 +10854,6 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10962,7 +10870,6 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10979,7 +10886,6 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10996,7 +10902,6 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11013,7 +10918,6 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11030,7 +10934,6 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11047,7 +10950,6 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11064,7 +10966,6 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11081,7 +10982,6 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11098,7 +10998,6 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11115,7 +11014,6 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11132,7 +11030,6 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11149,7 +11046,6 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11166,7 +11062,6 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11183,7 +11078,6 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11200,7 +11094,6 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11217,7 +11110,6 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11234,7 +11126,6 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11251,7 +11142,6 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11268,7 +11158,6 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11285,7 +11174,6 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11302,7 +11190,6 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11319,7 +11206,6 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11336,7 +11222,6 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11353,7 +11238,6 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11370,7 +11254,6 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11387,7 +11270,6 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11408,7 +11290,6 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11429,7 +11310,6 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11450,7 +11330,6 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11471,7 +11350,6 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11492,7 +11370,6 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11513,7 +11390,6 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11534,7 +11410,6 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11555,7 +11430,6 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11576,7 +11450,6 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11597,7 +11470,6 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11618,7 +11490,6 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11639,7 +11510,6 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11660,7 +11530,6 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11681,7 +11550,6 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11702,7 +11570,6 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11723,7 +11590,6 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11744,7 +11610,6 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11765,7 +11630,6 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11786,7 +11650,6 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11807,7 +11670,6 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11828,7 +11690,6 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11849,7 +11710,6 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11870,7 +11730,6 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11891,7 +11750,6 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11912,7 +11770,6 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11929,7 +11786,6 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11950,7 +11806,6 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11971,7 +11826,6 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11992,7 +11846,6 @@
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12013,7 +11866,6 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12030,7 +11882,6 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12047,7 +11898,6 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12064,7 +11914,6 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12081,7 +11930,6 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12098,7 +11946,6 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12115,7 +11962,6 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12132,7 +11978,6 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12149,7 +11994,6 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12166,7 +12010,6 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12183,7 +12026,6 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12200,7 +12042,6 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12217,7 +12058,6 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12234,7 +12074,6 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -12251,7 +12090,6 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12272,7 +12110,6 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -12293,7 +12130,6 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -12314,7 +12150,6 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12335,7 +12170,6 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12356,7 +12190,6 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12377,7 +12210,6 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12398,7 +12230,6 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12419,7 +12250,6 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12440,7 +12270,6 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12461,7 +12290,6 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12482,7 +12310,6 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12503,7 +12330,6 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12524,7 +12350,6 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12545,7 +12370,6 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12566,7 +12390,6 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12587,7 +12410,6 @@
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12608,7 +12430,6 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12629,7 +12450,6 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12650,7 +12470,6 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12671,7 +12490,6 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12692,7 +12510,6 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12713,7 +12530,6 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12734,7 +12550,6 @@
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12755,7 +12570,6 @@
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12776,7 +12590,6 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12797,7 +12610,6 @@
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12818,7 +12630,6 @@
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12839,7 +12650,6 @@
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12860,7 +12670,6 @@
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12881,7 +12690,6 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12902,7 +12710,6 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12923,7 +12730,6 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12944,7 +12750,6 @@
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12965,7 +12770,6 @@
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12986,7 +12790,6 @@
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13007,7 +12810,6 @@
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13028,7 +12830,6 @@
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13049,7 +12850,6 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13070,7 +12870,6 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13087,7 +12886,6 @@
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13108,7 +12906,6 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13125,7 +12922,6 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13142,7 +12938,6 @@
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13163,7 +12958,6 @@
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13184,7 +12978,6 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13205,7 +12998,6 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13226,7 +13018,6 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13247,7 +13038,6 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13268,7 +13058,6 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13289,7 +13078,6 @@
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13310,7 +13098,6 @@
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13331,7 +13118,6 @@
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13352,7 +13138,6 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13369,7 +13154,6 @@
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13390,7 +13174,6 @@
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13411,7 +13194,6 @@
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13432,7 +13214,6 @@
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13449,7 +13230,6 @@
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13466,7 +13246,6 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13487,7 +13266,6 @@
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13508,7 +13286,6 @@
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13529,7 +13306,6 @@
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13550,7 +13326,6 @@
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13571,7 +13346,6 @@
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13592,7 +13366,6 @@
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13613,7 +13386,6 @@
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13630,7 +13402,6 @@
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13647,7 +13418,6 @@
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13668,7 +13438,6 @@
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13685,7 +13454,6 @@
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13702,7 +13470,6 @@
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13723,7 +13490,6 @@
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13744,7 +13510,6 @@
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13765,7 +13530,6 @@
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13786,7 +13550,6 @@
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13807,7 +13570,6 @@
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13828,7 +13590,6 @@
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13849,7 +13610,6 @@
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13870,7 +13630,6 @@
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13891,7 +13650,6 @@
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13912,7 +13670,6 @@
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13933,7 +13690,6 @@
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13954,7 +13710,6 @@
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13975,7 +13730,6 @@
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13996,7 +13750,6 @@
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14017,7 +13770,6 @@
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14038,7 +13790,6 @@
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14059,7 +13810,6 @@
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14080,7 +13830,6 @@
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14101,7 +13850,6 @@
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14122,7 +13870,6 @@
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14143,7 +13890,6 @@
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14164,7 +13910,6 @@
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14185,7 +13930,6 @@
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14206,7 +13950,6 @@
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14227,7 +13970,6 @@
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14248,7 +13990,6 @@
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14269,7 +14010,6 @@
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14290,7 +14030,6 @@
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14311,7 +14050,6 @@
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14332,7 +14070,6 @@
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14353,7 +14090,6 @@
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14374,7 +14110,6 @@
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14395,7 +14130,6 @@
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14416,7 +14150,6 @@
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14437,7 +14170,6 @@
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14458,7 +14190,6 @@
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14475,7 +14206,6 @@
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14492,7 +14222,6 @@
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14509,7 +14238,6 @@
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14526,7 +14254,6 @@
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14543,7 +14270,6 @@
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14560,7 +14286,6 @@
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14577,7 +14302,6 @@
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14594,7 +14318,6 @@
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14611,7 +14334,6 @@
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14628,7 +14350,6 @@
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14649,7 +14370,6 @@
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14670,7 +14390,6 @@
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14691,7 +14410,6 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14712,7 +14430,6 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14733,7 +14450,6 @@
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14754,7 +14470,6 @@
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14775,7 +14490,6 @@
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14796,7 +14510,6 @@
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14817,7 +14530,6 @@
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14838,7 +14550,6 @@
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14859,7 +14570,6 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14880,7 +14590,6 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14901,7 +14610,6 @@
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14922,7 +14630,6 @@
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14943,7 +14650,6 @@
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14964,7 +14670,6 @@
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14985,7 +14690,6 @@
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15006,7 +14710,6 @@
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15027,7 +14730,6 @@
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15048,7 +14750,6 @@
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15069,7 +14770,6 @@
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15090,7 +14790,6 @@
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15111,7 +14810,6 @@
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15132,7 +14830,6 @@
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15153,7 +14850,6 @@
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15174,7 +14870,6 @@
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15195,7 +14890,6 @@
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15216,7 +14910,6 @@
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15237,7 +14930,6 @@
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15258,7 +14950,6 @@
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15279,7 +14970,6 @@
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15300,7 +14990,6 @@
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15321,7 +15010,6 @@
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15342,7 +15030,6 @@
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15363,7 +15050,6 @@
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15384,7 +15070,6 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15405,7 +15090,6 @@
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15426,7 +15110,6 @@
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15447,7 +15130,6 @@
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15468,7 +15150,6 @@
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15489,7 +15170,6 @@
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15510,7 +15190,6 @@
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15531,7 +15210,6 @@
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15552,7 +15230,6 @@
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15573,7 +15250,6 @@
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -15594,7 +15270,6 @@
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -15615,7 +15290,6 @@
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15636,7 +15310,6 @@
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15657,7 +15330,6 @@
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15678,7 +15350,6 @@
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15699,7 +15370,6 @@
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15720,7 +15390,6 @@
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15741,7 +15410,6 @@
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15762,7 +15430,6 @@
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15783,7 +15450,6 @@
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15804,7 +15470,6 @@
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15825,7 +15490,6 @@
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15846,7 +15510,6 @@
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15867,7 +15530,6 @@
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15888,7 +15550,6 @@
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15909,7 +15570,6 @@
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15930,7 +15590,6 @@
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15951,7 +15610,6 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15972,7 +15630,6 @@
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -15993,7 +15650,6 @@
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16014,7 +15670,6 @@
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16035,7 +15690,6 @@
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -16056,7 +15710,6 @@
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -16077,7 +15730,6 @@
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16098,7 +15750,6 @@
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -16115,7 +15766,6 @@
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr"/>
       <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -16132,7 +15782,6 @@
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16149,7 +15798,6 @@
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16166,7 +15814,6 @@
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16183,7 +15830,6 @@
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16200,7 +15846,6 @@
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -16221,7 +15866,6 @@
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -16242,7 +15886,6 @@
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -16263,7 +15906,6 @@
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -16284,7 +15926,6 @@
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -16305,7 +15946,6 @@
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -16322,7 +15962,6 @@
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -16339,7 +15978,6 @@
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -16356,7 +15994,6 @@
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -16377,7 +16014,6 @@
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -16398,7 +16034,6 @@
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16419,7 +16054,6 @@
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -16440,7 +16074,6 @@
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -16461,7 +16094,6 @@
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -16482,7 +16114,6 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16503,7 +16134,6 @@
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -16524,7 +16154,6 @@
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -16545,7 +16174,6 @@
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -16566,7 +16194,6 @@
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -16587,7 +16214,6 @@
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -16608,7 +16234,6 @@
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -16629,7 +16254,6 @@
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -16650,7 +16274,6 @@
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -16671,7 +16294,6 @@
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -16692,7 +16314,6 @@
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -16713,7 +16334,6 @@
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -16734,7 +16354,6 @@
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -16755,7 +16374,6 @@
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -16776,7 +16394,6 @@
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -16797,7 +16414,6 @@
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -16818,7 +16434,6 @@
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -16839,7 +16454,6 @@
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -16860,7 +16474,6 @@
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -16881,7 +16494,6 @@
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -16902,7 +16514,6 @@
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -16923,7 +16534,6 @@
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -16944,7 +16554,6 @@
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -16965,7 +16574,6 @@
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -16986,7 +16594,6 @@
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -17007,7 +16614,6 @@
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -17028,7 +16634,6 @@
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -17049,7 +16654,6 @@
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -17070,7 +16674,6 @@
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -17091,7 +16694,6 @@
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -17112,7 +16714,6 @@
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17133,7 +16734,6 @@
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -17154,7 +16754,6 @@
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -17175,7 +16774,6 @@
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -17196,7 +16794,6 @@
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -17217,7 +16814,6 @@
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -17238,7 +16834,6 @@
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -17259,7 +16854,6 @@
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -17280,7 +16874,3911 @@
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C299"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Imagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LAPTOP PREDATOR ELIOS I7-13</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ALCATEL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A31 PRIME</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALCATEL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MODEL 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11 NORMAL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11 PRO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12 MINI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12 NORMAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12 PRO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13 MINI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13 NORMAL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13 PRO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14 NORMAL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14 NORMAL SIM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14 PLUS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14 PLUS SIM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14 PRO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>14 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14 PRO MAX SIM</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14 PRO SIM</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>15 NORMAL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>15 NORMAL SIM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>15 PLUS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>15 PLUS SIM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>15 PRO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>15 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>15 PRO MAX SIM</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>15 PRO SIM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16 E</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>16 NORMAL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>16 NORMAL SIM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>16 NORMAL VERD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16 PLUS</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16 PLUS SIM</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16 PRO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16 PRO MAX SIM</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16E</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17 AIR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>17 NORMAL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>17 PRO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>17 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>17 PRO MAX SIM</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AIRPODS 4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AIRPODS 4 CANCELACION</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AIRPODS PRO 2 LIGHTNING</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AIRPODS PRO 2 TIPO C</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AIRPODS PRO 3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AIRTAG PACK</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>APPLE PENCIL (USB-C)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>APPLE PENCIL 2GEN</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>APPLE PENCIL PRO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S10 42MM</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S10 42MM ROSEGOLD</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S10 46MM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S10 46MM ROSEGOLD</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S11 42MM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S11 46MM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S9 41MM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>APPLEWATCH S9 45MM</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>APPLEWATCH SE 2 40MM STARLIGHT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>APPLEWATCH SE 2 44MM</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>APPLEWATCH SE 2 44MM STARLIGHT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>APPLEWATCH SE 3 40MM STARLIGHT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>APPLEWATCH SE 3 44MM MIDNIGHT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>APPLEWATCH SE 3 44MM STARLIGHT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>APPLEWATCH ULTRA 2 49MM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>APPLEWATCH ULTRA 3 49MM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>APPLEWATCH ULTRA 49MM</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CUBO 20W ORIGINAL</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CUBO 40W ORIGINAL</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>IPAD 10MA DATOS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>IPAD 10MA WIFI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>IPAD 10MA WIFI AMARILLA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IPAD 11VA WIFI</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>IPAD 9NA WIFI</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>IPAD AIR 5TA WIFI</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IPAD AIR M3 11PLG DATOS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IPAD AIR M3 11PLG WIFI</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>IPAD AIR M3 13PLG WIFI</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>IPAD AIR M4 11PLG WIFI</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IPAD MINI 6TA DATOS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IPAD MINI 6TA WIFI</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>IPAD PRO 6TA GEN M2 13PLG WIFI</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IPAD PRO M1 13PLG DATOS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IPAD PRO M4 11PLG WIFI</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IPAD PRO M4 13PLG DATOS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>IPAD PRO M4 14PLG WIFI</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MACBOOK AIR 15” M5</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MACBOOK AIR M4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MACBOOK AIR M4 STARLIGHT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MACBOOK NEO 13”</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MAGIC KEYBOARD PARA IPAD AIR 11" 4TA GEN, 5TA GEN, M2, M3, M4</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SE 3</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SE 3.ª GEN</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>XS MAX</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 AIR IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 NORMAL CLEAR IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO CLEAR IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX CARBON GRAPHITE IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX CLEAR IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX FOREST GREEN IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX GLACIER IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX MIDNIGHT IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX SAND IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX SOLAR ORANGE IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>COBERTOR S26 ULTRA BLACK CLEAR IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>COBERTOR S26 ULTRA CLEAR IMPACT HYBRID SERIES</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>VIDRIO TEMPLADO 17 PRO MAX PRIVACIDAD</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ARTSCASE</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VIDRIO TEMPLADO 17 PRO MAX TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>BLU</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BMOBILE</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NOVUS 65</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>INSPIRON 3501 I5-10</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>200 LITE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HONOR 400</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HONOR 70</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HONOR 90</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>MAGIC5 LITE 5G</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MAGIC5 LITE 5G TORNASOL</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MAGIC7 LITE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MAGIC8 LITE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PLAY10</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PLAY10 A</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PLAY9 A</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>X5B</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>X6B</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>X7C /8GB</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>X8A</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>X8B</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>HOTWAV</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>A17 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HP LAPTOP I5-12</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HP LAPTOP I5-13</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>GT 30 PRO</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HOT 50I</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HOT 60 PRO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HOT 60 PRO PLUS</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HOT 60I</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HOT 70</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NOTE 50 PRO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SMART 10</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SMART 20</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>INFINIX</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SMART 9</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ITEL</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>A80</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>JBL</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>G04</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>LENOVO</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>TAB M8</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SMART TV LG 32" THINQ AI 32LR65</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SMART TV LG 65" QNED AI 4K/ 65-QNED73A</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>LOGIC</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>L65A</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>LOGIC</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>L66M</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>LOGIC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>L68 ULTRA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>M-HORSE</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HOT 40 PRO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MAXWEST</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>NITRO 55A</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>E7I</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>G15</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MOTOROLA</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>G9 PLUS</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>NEWPAD</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>NEWPAD 10 DATOS</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>NINTENDO</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DONKEY KONG BANANZA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>NINTENDO</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SWITCH 2</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>NINTENDO</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SWITCH 2 MARIO KART</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>NINTENDO</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SWITCH OLED</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>OLAX</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>8 ULTRA SMART WATCH 49MM</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OLAX</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>MINI DC UPS</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OPPO</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>OPPO</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>OPPO</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>RENO 11 5G</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>OPPO</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>RENO 12 5G</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>OPPO</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>RENO 12F 5G</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OPPO</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>RENO 7</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PLAYSTATION</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EA FC 26</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PLAYSTATION</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PS5 DIGITAL SLIM</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PLAYSTATION</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PS5 DIGITAL SLIM COD BLACK OPS 6</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PLAYSTATION</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PS5 DIGITAL SLIM FORTNITE</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PLAYSTATION</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PS5 DISCO SLIM</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PLAYSTATION</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PS5 DISCO SLIM FORTNITE</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>QLINK</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SCEPTER 8 WIFI</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>REALME</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>C61</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>A04E</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>A16 4G</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>A16 5G</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>A17 4G</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>A17 5G</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>A35 5G</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>A37 5G</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>A55</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>A56</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>A57 5G</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>A57 5G HIELO</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>BORRAR</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>BUDS 3 PRO</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BUDS 4</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>BUDS 4 PRO</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>BUDS FE</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CABLE C A C</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CARGADOR 45W COMPLETO ORIGINAL</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CUBO 25W ORIGINAL</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>GALAXY FIT 3</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>GALAXY WATCH ULTRA 47MM</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>J3 PRIME</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>NOTE 10 PLUS</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>NOTE 20 ULTRA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>S10 NORMAL</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>S10 PLUS</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>S10E</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>S20 FE</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>S20 ULTRA</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>S21 NORMAL</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>S21 PLUS</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>S21 ULTRA</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>S22 NORMAL</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>S22 PLUS</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>S22 ULTRA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>S23 FE</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>S23 NORMAL</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>S23 PLUS</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>S23 ULTRA</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>S23 ULTRA LIMA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>S24 FE</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>S24 NORMAL</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>S24 PLUS</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>S24 PLUS GB/12RAM</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>S24 ULTRA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>S25 FE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>S25 NORMAL</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>S25 NORMAL HIELO</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>S25 PLUS</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>S25 ULTRA</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>S25 ULTRA ROSA</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>S26 NORMAL</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>S26 PLUS</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>S26 ULTRA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TAB A11 PLUS 5G WIFI</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>TAB A7 LITE DATOS</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>TAB A7 LITE WIFI</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>TAB A8 WIFI</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>TAB A9 PLUS 5G DATOS</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>TAB A9 PLUS 5G WIFI</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>TAB A9 PLUS WIFI</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>TAB A9 WIFI</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TAB S10 FE</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>TAB S10 FE PLUS</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TAB S5E DATOS</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TAB S5E WIFI</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TAB S7 WIFI</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TAB S8 WIFI</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TAB S9 FE</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>WATCH 7 40MM</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>WATCH 7 44M</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>WATCH 8 40MM</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>WATCH 8 44MM</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>WATCH 8 CLASSIC 46MM</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>WATCH ACTIVE 2 40MM</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Z FLIP 7</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Z FLIP 7 FE</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SKY</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ELITE P55 MAX</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SKY</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>PAD 10 MAX DATOS</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SPIGEN</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>COBERTOR 16 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SPIGEN</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>COBERTOR 17 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SPIGEN</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>COBERTOR S26 ULTRA</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>TAB 8 PLUS DATOS</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>CAMON 19 NEO</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SPARK 20 PRO PLUS</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SPARK 20C</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SPARK GO 1</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SPARK GO 1S</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SPARK GO 2</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>SPARK GO 2023</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>TECNO</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SPARK GO 2024</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>VORTEX</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ZG55</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>WIKO</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>WIKO T10</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>15T</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>NOTE 13 PRO PLUS</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>NOTE 14</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>NOTE 14 PRO</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>NOTE 14 PRO PLUS</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>POCO F6 PRO</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>POCO X7</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>POCO X7 PRO</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>POCO X8 PRO</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>POCO X8 PRO MAX</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>REDMI 14C</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>REDMI 15</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>REDMI 15C</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>REDMI A5</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 15</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 15 PRO</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>XIAOMI</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>REDMI NOTE 15 PRO PLUS 5G</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>BLADE A36</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/apps-script/Estructura_PreGenerada.xlsx
+++ b/apps-script/Estructura_PreGenerada.xlsx
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>1 SIM</t>
         </is>
       </c>
     </row>

--- a/apps-script/Estructura_PreGenerada.xlsx
+++ b/apps-script/Estructura_PreGenerada.xlsx
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1 SIM</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
